--- a/AAII_Financials/Quarterly/BNTX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNTX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="92">
   <si>
     <t>BNTX</t>
   </si>
@@ -656,143 +656,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="36" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43281</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
@@ -802,101 +803,104 @@
       <c r="AJ7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>120600</v>
+      </c>
+      <c r="E8" s="3">
         <v>136200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1065400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1782100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>306300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>197600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1232000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1388400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>137900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>202400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1634800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>947600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>183100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1387400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4738600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3740500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3478100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6936200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5997800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6555400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5616400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2167200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>344500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>70100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>45600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>30200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>126800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>63600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>150100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>51100</v>
       </c>
-      <c r="AG8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
@@ -906,101 +910,104 @@
       <c r="AJ8" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK8" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E9" s="3">
         <v>82300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>355500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>174000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>89700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>90600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>252100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>199500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>64100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>63800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>198000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>171300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>177800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>104300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>203200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>813600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>832000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1408100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>632200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1304600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>935100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>246600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>40900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>7100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>6200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>6400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>20300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>16100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>7600</v>
       </c>
-      <c r="AG9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,101 +1017,104 @@
       <c r="AJ9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E10" s="3">
         <v>53800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>709900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1608100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>216600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>107000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>979900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1188800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>73800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>138600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1436800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>776400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1283100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4535400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2927000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2646200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>5528100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>5365500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>5250900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>4681300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1920600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>303600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>63000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>39400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>23800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>106500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>52900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>134000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>43500</v>
       </c>
-      <c r="AG10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1114,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1152,101 +1165,102 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>545100</v>
+      </c>
+      <c r="E12" s="3">
         <v>642200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>593400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>662700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>597900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>568100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>633400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>613800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>626400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>547500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>638700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>527000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>407600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>362900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>549900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>354700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>422200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>299200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>283700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>271300</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>205300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>220800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>256300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>236300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>103800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>71000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>264400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>135500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>168300</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>68800</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1256,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1360,77 +1377,80 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>24500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>18800</v>
       </c>
-      <c r="G14" s="3">
-        <v>27500</v>
-      </c>
       <c r="H14" s="3">
+        <v>35100</v>
+      </c>
+      <c r="I14" s="3">
         <v>-16200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>30600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>46000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>23300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>22900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-1300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-52400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-22500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-71800</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,8 +1460,8 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1464,77 +1484,80 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>304000</v>
+      </c>
+      <c r="E15" s="3">
         <v>139900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>41900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>145700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>59900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>46300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>124000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>53500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>37100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>43700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>34800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>34100</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>14700</v>
       </c>
       <c r="R15" s="3">
         <v>14700</v>
       </c>
       <c r="S15" s="3">
+        <v>14700</v>
+      </c>
+      <c r="T15" s="3">
         <v>12600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>11800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>13800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>11100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>8900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>7900</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1544,8 +1567,8 @@
       <c r="AB15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1568,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1603,101 +1629,102 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1093800</v>
+      </c>
+      <c r="E17" s="3">
         <v>921400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1420700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1820800</v>
       </c>
-      <c r="G17" s="3">
-        <v>819100</v>
-      </c>
       <c r="H17" s="3">
+        <v>811500</v>
+      </c>
+      <c r="I17" s="3">
         <v>776200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1067900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1365000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1168400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>745200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>523400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>892100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>717100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>541600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1091400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1160300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1073800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1764800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>902800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1468700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1174500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>408600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>101000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>263500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>133900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>94800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>338700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>176000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>213400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>86100</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1707,101 +1734,104 @@
       <c r="AJ17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-973200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-785200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-355300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-38700</v>
       </c>
-      <c r="G18" s="3">
-        <v>-512900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-505200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-578600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>164100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1030500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-542800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1111400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>55500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-534100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>845800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3647200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2580200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2404300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5171400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>5094900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5086700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4441900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1758600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>243500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-193400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-88300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-64600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-211900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-112400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-63300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-35100</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1811,8 +1841,11 @@
       <c r="AJ18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1849,101 +1882,102 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-12800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-64000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>198900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-89500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-75200</v>
-      </c>
       <c r="H20" s="3">
+        <v>9200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>272500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-205600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-195500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-212800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>359700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-193100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-88600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>67400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-130900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>65700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>125700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>293200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>19100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-59600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-185300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-20300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-37900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-21400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>9300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>8700</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1953,101 +1987,104 @@
       <c r="AJ20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-656300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-581300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-512300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>196500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-377800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-454500</v>
+      </c>
+      <c r="I21" s="3">
         <v>-530600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>15600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>278400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-781500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-288700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>788900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>292200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-410600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>812600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3548400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2682100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2566100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5494700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5142200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5048500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4274000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1752000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>218200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-205700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-88600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-48400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-167900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-91100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-28200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2057,101 +2094,104 @@
       <c r="AJ21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-3400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3100</v>
       </c>
-      <c r="G22" s="3">
-        <v>7800</v>
-      </c>
       <c r="H22" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I22" s="3">
         <v>4000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5900</v>
-      </c>
-      <c r="K22" s="3">
-        <v>5100</v>
       </c>
       <c r="L22" s="3">
         <v>5100</v>
       </c>
       <c r="M22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="N22" s="3">
         <v>3800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>4500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>6300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>700</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>600</v>
       </c>
       <c r="Z22" s="3">
         <v>600</v>
       </c>
       <c r="AA22" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AB22" s="3">
         <v>500</v>
       </c>
       <c r="AC22" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD22" s="3">
         <v>2000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>1000</v>
       </c>
-      <c r="AG22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,101 +2201,104 @@
       <c r="AJ22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-981000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-655000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-267000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-472900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-481400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>311800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>177000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-863400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-358000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>733100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>240700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-450000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>768900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3514000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2641300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2523600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5460200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5110300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5026300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4256100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1737600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>205100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-215400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-98700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-209500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-111300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-56100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-27400</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2265,100 +2308,103 @@
       <c r="AJ23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-43300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-41700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>91100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>62700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-18900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-32000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>43200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-43900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-18000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>226900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>70700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-242100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>223300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>990100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>712400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>704300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1435500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1677900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1568400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1307300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>544000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-160900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-300</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="3" t="s">
-        <v>3</v>
+      <c r="AG24" s="3">
+        <v>0</v>
       </c>
       <c r="AH24" s="3" t="s">
         <v>3</v>
@@ -2369,8 +2415,11 @@
       <c r="AJ24" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK24" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2473,101 +2522,104 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-937700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-613300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-358100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-33700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-454000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-449400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>268700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>220900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-865500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-340000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>506100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>170000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-207900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>545600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2523900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1928900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1819300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4024700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3432500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3457900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2948900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1193500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>366000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-218000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-96300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-209200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-111300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-56800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-27400</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2577,101 +2629,104 @@
       <c r="AJ26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-937700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-613300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-358100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-33700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-454000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-449400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>268700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>220900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-865500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-340000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>506100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>170000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-207900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>545600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2523900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1928900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1819300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4024700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3432500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3457900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2948900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1193500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>366000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-218000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-96300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-209000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-111100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-56500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-27300</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2681,8 +2736,11 @@
       <c r="AJ27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2889,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,101 +3164,104 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E32" s="3">
         <v>64000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-198900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>89500</v>
       </c>
-      <c r="G32" s="3">
-        <v>75200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="I32" s="3">
         <v>1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-272500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>205600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>195500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>212800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-359700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>193100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>88600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-67400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>130900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-65700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-125700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-293200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-19100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>59600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>185300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>20300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>37900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>21400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>10000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-9300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-8700</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,101 +3271,104 @@
       <c r="AJ32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-937700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-613300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-358100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-33700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-454000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-449400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>268700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>220900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-865500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-340000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>506100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>170000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-207900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>545600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2523900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1928900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1819300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4024700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3432500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3457900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2948900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1193500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>366000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-218000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-96300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-209000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-111100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-56500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-27300</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,8 +3378,11 @@
       <c r="AJ33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3409,101 +3485,104 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-937700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-613300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-358100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-33700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-454000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-449400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>268700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>220900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-865500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-340000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>506100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>170000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-207900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>545600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2523900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1928900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1819300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4024700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3432500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3457900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2948900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1193500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>366000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-218000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-96300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-209000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-111100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-56500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-27300</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3513,106 +3592,109 @@
       <c r="AJ35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43281</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3622,8 +3704,11 @@
       <c r="AJ38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3660,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3698,95 +3784,96 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11128800</v>
+      </c>
+      <c r="E41" s="3">
         <v>11460200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9011900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11842000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12060500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11008300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10106500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10734600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11118300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9684500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12892300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14284300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15465700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13194200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15368100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14507000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10157200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6707200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1835100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2576700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>967100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>943200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1207100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1028000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>625100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>492700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>606100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>349000</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,95 +3889,98 @@
       <c r="AJ41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4253300</v>
+      </c>
+      <c r="E42" s="3">
         <v>4343600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7121300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5016700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3951300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3828400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6297100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7895300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7413500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7217500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>5399900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2384900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1518200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>389000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>209800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>413700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>136900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>18500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>233500</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3906,95 +3996,98 @@
       <c r="AJ42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>280100</v>
+      </c>
+      <c r="E43" s="3">
         <v>705900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1156400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>920500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1699000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1110000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1577700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1336200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>307000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2077000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2586200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2432400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3270100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7593200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>7914900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>7899700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11298100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13814700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13423400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>11420300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7461700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2535000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>165900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>11200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>13600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>14800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11400</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4010,95 +4103,98 @@
       <c r="AJ43" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E44" s="3">
         <v>119700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>130000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>264800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>270900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>275000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>293300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>338100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>364400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>372600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>395400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>440000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>490100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>460800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>486900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>318600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>400100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>499800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>544800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>423700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>323100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>155400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>64000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>12800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>9400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>10500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>13700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>8900</v>
       </c>
-      <c r="AE44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4114,95 +4210,98 @@
       <c r="AJ44" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1699500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1278900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1538600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>530200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>725400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>667100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1192700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>314100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>385000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>363600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>310500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>302900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>231800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>186100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>301200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>254700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>133000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>158400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>122900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>170900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>176300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>107000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>88700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>65700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>29700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>19000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>17400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14900</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,95 +4317,98 @@
       <c r="AJ45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17476600</v>
+      </c>
+      <c r="E46" s="3">
         <v>17908200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18958100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>18574100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18707100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16888800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19467300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20618100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19588100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19715300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21584300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>19844500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20975900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21823200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>24280800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>22985200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>21988400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>21181100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16339900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14593500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>8929000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3741100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1662600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1133200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>677600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>537700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>653900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>617800</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4322,68 +4424,71 @@
       <c r="AJ46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2112000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2481300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2881500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2905100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2941600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2428100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1255900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1485800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1485200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1712400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1300000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1368200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1500300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>561500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>88800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>57100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>56000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>52700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>23100</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4501,8 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -4408,8 +4513,8 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-      <c r="AE47" s="3" t="s">
-        <v>3</v>
+      <c r="AE47" s="3">
+        <v>0</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>3</v>
@@ -4426,95 +4531,98 @@
       <c r="AJ47" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK47" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1391900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1519900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1515900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1455700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1458700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1370500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1225200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1293100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1205400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1112200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1073900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>980000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>976000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>920900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>909500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>821900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>722600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>606000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>564200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>476100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>403200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>381700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>325100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>190500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>183000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>158600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>172800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>150700</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,95 +4638,98 @@
       <c r="AJ48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2050600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2210700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2317600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2050300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2173900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2039700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1212300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1391800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1322900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1284300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1264700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1091300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>547400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>411300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>243300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>244500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>240900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>235000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>219400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>175400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>173600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>174800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>163100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>175100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>199900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>102500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>104400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>116400</v>
       </c>
-      <c r="AE49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4634,8 +4745,11 @@
       <c r="AJ49" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4738,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4842,86 +4959,89 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>191700</v>
+      </c>
+      <c r="E52" s="3">
         <v>161500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>126000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>28900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>31500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>66900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>69600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>94600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>115900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>89800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>116900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>261500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>380700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>13300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>15600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>82100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>173600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>151000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>161900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1400</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4937,8 +5057,8 @@
       <c r="AG52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH52" s="3">
-        <v>0</v>
+      <c r="AH52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI52" s="3">
         <v>0</v>
@@ -4946,8 +5066,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5050,95 +5173,98 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23240700</v>
+      </c>
+      <c r="E54" s="3">
         <v>24298500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25817300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25039400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>25411200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22894900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23325100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>24984600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23827200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>24012100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25429800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23504700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24263800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23988500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25783900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24489300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23019200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22088000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17162200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15327100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>9679400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4448600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2312600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1504200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1061900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>798800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>931200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>884900</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5154,8 +5280,11 @@
       <c r="AJ54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5192,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5230,95 +5360,96 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>738800</v>
+      </c>
+      <c r="E57" s="3">
         <v>540500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>628000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>469100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>592100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>479700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>441800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>850500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>944500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>322400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>391300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>235700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>249600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>32500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>226100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>320400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>316700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>134600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>173500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>278800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>277900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>112400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>102000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>43500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>38900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>23900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>20700</v>
       </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5334,95 +5465,98 @@
       <c r="AJ57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E58" s="3">
         <v>65400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>61300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>62700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>61500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>60000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>40900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>41700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>37800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>33800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>31100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>42300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>42100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>40600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>39900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>40000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>35100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>33300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>140800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>20500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>14700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>19000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>6100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>140300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>39700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>17800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>25000</v>
       </c>
-      <c r="AE58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5438,95 +5572,98 @@
       <c r="AJ58" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK58" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1422700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1429100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1826000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2075900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1519900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1118900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2129600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1921100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1617000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1376500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1866300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1634700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1694100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1611900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3002100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3916700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3917500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4026200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3460100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4980300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3054100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1255700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>496300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>94900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>148900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>116000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>133300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>120900</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5542,95 +5679,98 @@
       <c r="AJ59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2226900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2035100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2515300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2607600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2173600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1658600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2612300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2813400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2599300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1732700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2288600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1912800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1985800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1685000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3268100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4277100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4269400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4194100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3774400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>5279600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3346800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1387100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>604400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>278700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>227500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>155000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>161300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>166600</v>
       </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5646,95 +5786,98 @@
       <c r="AJ60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>295800</v>
+      </c>
+      <c r="E61" s="3">
         <v>283800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>252700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>225300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>255100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>256700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>222300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>230100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>235000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>221200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>211100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>171400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>182400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>187300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>195200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>256100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>224800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>169100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>186000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>288300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>257000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>250300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>230400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>182300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>76700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>72700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>80400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>75100</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
@@ -5750,95 +5893,98 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>292600</v>
+      </c>
+      <c r="E62" s="3">
         <v>259000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>275400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>241800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>291600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>277600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>160800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>159700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>138200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>63700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>67100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>63700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>42900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>107100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>107600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>211500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>412400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>307800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>377800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>274900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>145400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>109400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>80400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>101100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>82200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>113400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>172200</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6000,11 @@
       <c r="AJ62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5958,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6062,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6166,95 +6321,98 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2953400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2739900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3245700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3360100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3678800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2438200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3228700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3665700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3391800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2469100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3051200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2477100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2531800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1970600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3570300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4640900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4705700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4775600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4268200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5945700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3878600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1782800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>944300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>541300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>405300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>309900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>355100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>413900</v>
       </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
@@ -6270,8 +6428,11 @@
       <c r="AJ66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6308,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6412,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6516,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6620,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6724,95 +6895,98 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18975400</v>
+      </c>
+      <c r="E72" s="3">
         <v>20096900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>21089500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21432500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21486300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>20192600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>19772200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>21011000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19972600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20982000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21845100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20433300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20900400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21007400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>21944100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>19590900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>18049400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>17048000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12631100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>9120300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5544200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2410200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1127400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>712900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>402800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>241500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>311400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>210400</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6828,8 +7002,11 @@
       <c r="AJ72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6932,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7036,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7140,95 +7323,98 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20287300</v>
+      </c>
+      <c r="E76" s="3">
         <v>21558600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22571600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>21679300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>21732400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20456800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20096400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>21318900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20435300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21543000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22378600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21027500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21732000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22017900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22213600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19848500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18313500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17312400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12894000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9381400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5800800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2665700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1368300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>962800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>656700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>488900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>576100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>471000</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7244,8 +7430,11 @@
       <c r="AJ76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7348,106 +7537,109 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43281</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7457,101 +7649,104 @@
       <c r="AJ80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-937700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-613300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-358100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-33700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-454000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-449400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>268700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>220900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-865500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-340000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>506100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>170000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-207900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>545600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2523900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1928900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1819300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4024700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3432500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3457900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2948900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1193500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>366000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-218000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-96300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-209000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-111100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-56500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-27300</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7561,8 +7756,11 @@
       <c r="AJ81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7599,101 +7797,102 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E83" s="3">
         <v>46300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>49500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>53500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>41300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>43700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>34700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>32100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>36200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>36100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>30000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>28200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>21300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>13800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>12500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>9100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>9600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>9400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>39600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>19100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>25900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>10300</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
@@ -7703,8 +7902,11 @@
       <c r="AJ83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7807,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7911,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8015,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8119,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8223,101 +8437,104 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-485400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>363400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>916000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>172000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-843800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-479700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-712600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1743500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-342300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>940500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>858600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4789000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-736000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>918400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5164600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4264400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4407000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-216300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1616200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-106100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-329400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>248600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-199800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-16900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-59700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-231800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-105000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-68400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-82000</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8327,8 +8544,11 @@
       <c r="AJ89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8365,101 +8585,102 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-65500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-74200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-42100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-31800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-52900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-69000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-81200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-94900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-63100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-92500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-57200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-73400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-144500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-82600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-75400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-60800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-53400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-41300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-23000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-25300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-45100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-35200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-14500</v>
       </c>
-      <c r="AG91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
@@ -8469,8 +8690,11 @@
       <c r="AJ91" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK91" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8573,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8677,101 +8904,104 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-114400</v>
+      </c>
+      <c r="E94" s="3">
         <v>3056200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3200200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1085700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-75600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1347600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>628100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-158500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-258700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2486100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2979000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1304200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2502000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-799000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-178300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-90000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-85300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>312700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-506200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-44300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-31500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-29900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-99600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-21100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-90000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-56100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-46500</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
@@ -8781,8 +9011,11 @@
       <c r="AJ94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8819,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8863,8 +9097,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8923,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9027,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9131,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9235,101 +9478,104 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-124000</v>
+      </c>
+      <c r="E100" s="3">
         <v>30400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-13500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-15600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-24500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-14300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-329200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-178400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-316500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-71700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-706100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-850400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>87400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-53000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-5700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>161800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>116000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>654100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>159500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>447500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>6000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>429600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>267900</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9339,101 +9585,104 @@
       <c r="AJ100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-17400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>14100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-154500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>64800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>99600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-29400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-162000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>45800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>116600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>59400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-168500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>50500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>121300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>58200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>16600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>26100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>26900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-45900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3100</v>
       </c>
-      <c r="AG101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH101" s="3" t="s">
         <v>3</v>
       </c>
@@ -9443,101 +9692,104 @@
       <c r="AJ101" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AK101" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-230100</v>
+      </c>
+      <c r="E102" s="3">
         <v>2597300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2851900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-208400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>91600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>471500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>155000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-882400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1456800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2829500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2207300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-710000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2208200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1880900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4418900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3450000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4865300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-758900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1592300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-337200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>219200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>433300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>132500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-73700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>125700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-155100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>281600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>142600</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9545,6 +9797,9 @@
         <v>3</v>
       </c>
       <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
